--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -4912,7 +4912,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4920,11 +4920,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="J84" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K84" t="n">
+        <v>65.2175</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>-24.03</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5158,7 +5170,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5166,11 +5178,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="J89" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K89" t="n">
+        <v>11.1815</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>-24.72</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6916,7 +6940,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6924,11 +6948,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="J126" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K126" t="n">
+        <v>104.7755</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
+        <v>-22.06</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5680,7 +5680,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5688,11 +5688,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="K100" t="n">
+        <v>18.0975</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>-24.77</v>
+      </c>
+      <c r="N100" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6202,7 +6214,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6210,11 +6222,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="J111" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="K111" t="n">
+        <v>35.302</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>-24.15</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6898,7 +6922,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6906,11 +6930,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="J125" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="K125" t="n">
+        <v>177.308</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>-18.66</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5488,7 +5488,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5496,11 +5496,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="J96" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K96" t="n">
+        <v>18.4794</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>-38.89</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-8.06</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6826,7 +6838,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6834,11 +6846,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="J123" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K123" t="n">
+        <v>65.1605</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>-24.01</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7402,7 +7426,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7410,11 +7434,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="J135" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K135" t="n">
+        <v>39.465</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M135" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="N135" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5266,7 +5266,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5274,11 +5274,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="J91" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K91" t="n">
+        <v>69.89449999999999</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="N91" t="n">
+        <v>11.2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5788,7 +5800,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5796,11 +5808,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+      <c r="J102" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K102" t="n">
+        <v>35.937</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="N102" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6580,7 +6604,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6588,11 +6612,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="J118" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K118" t="n">
+        <v>77.197</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -7420,7 +7420,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7428,11 +7428,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="J134" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="K134" t="n">
+        <v>55.407</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M134" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="N134" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -4516,7 +4516,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4524,11 +4524,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="J76" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="K76" t="n">
+        <v>73.682</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>-23.27</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5974,7 +5974,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5982,11 +5982,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="J105" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="K105" t="n">
+        <v>22.6575</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>-23.85</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6016,7 +6028,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6024,11 +6036,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+      <c r="J106" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="K106" t="n">
+        <v>58.6055</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>-24.68</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -6190,7 +6190,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6198,11 +6198,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="J109" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="K109" t="n">
+        <v>128.06</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>-20.22</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5236,7 +5236,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5244,11 +5244,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="J90" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="K90" t="n">
+        <v>33.212</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>-24.47</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -7384,7 +7384,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7392,11 +7392,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="J132" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="K132" t="n">
+        <v>23.895</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M132" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="N132" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6426,11 +6426,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="J113" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="K113" t="n">
+        <v>13.889</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>-24.85</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5482,7 +5482,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5490,11 +5490,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="J95" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="K95" t="n">
+        <v>42.0885</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>-32.69</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-6.59</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5578,7 +5590,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5586,11 +5598,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="J97" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="K97" t="n">
+        <v>27.1256</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>-40.71</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-8.58</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -7336,7 +7336,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7344,11 +7344,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="J130" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="K130" t="n">
+        <v>30.2295</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M130" t="n">
+        <v>-24.47</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5448,11 +5448,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="J94" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="K94" t="n">
+        <v>18.5138</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>-43.59</v>
+      </c>
+      <c r="N94" t="n">
+        <v>-8.93</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5344,7 +5344,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5352,11 +5352,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="J92" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="K92" t="n">
+        <v>256.2815</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>-13.49</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7198,7 +7210,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7206,11 +7218,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="J127" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="K127" t="n">
+        <v>26.163</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="N127" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -7426,7 +7426,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7434,11 +7434,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="J131" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K131" t="n">
+        <v>152.4705</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>-21.78</v>
+      </c>
+      <c r="N131" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -4828,7 +4828,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4836,11 +4836,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="J82" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="K82" t="n">
+        <v>220.407</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="N82" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5830,7 +5842,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5838,11 +5850,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="J101" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="K101" t="n">
+        <v>10.4502</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>-44.71</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-9.050000000000001</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -7924,7 +7924,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7932,11 +7932,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="J140" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K140" t="n">
+        <v>10.6785</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M140" t="n">
+        <v>-24.92</v>
+      </c>
+      <c r="N140" t="n">
+        <v>-5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/portfolio_log.xlsx
+++ b/data/portfolio_log.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5052,11 +5052,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K86" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="N86" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
